--- a/projects/project-3/assignment/src/data/ccom-qudt-structural-matches.xlsx
+++ b/projects/project-3/assignment/src/data/ccom-qudt-structural-matches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,110 @@
           <t>right_axioms</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#LengthUnit</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Length Unit</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000844</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Temperature</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#TemperatureUnit</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Temperature Unit</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#VolumeUnit</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Volume Unit</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000497</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Force</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ForceUnit</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Force Unit</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
